--- a/data/dataset/tables/удила.xlsx
+++ b/data/dataset/tables/удила.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="удила" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="удила" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'удила'!$A$1:$H$95</definedName>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.140625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -470,11 +470,6 @@
           <t>тип_окончания</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>шарнирность</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -502,12 +497,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>кольцевидно-овальное</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
@@ -537,12 +527,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>кольцевидно-овальное</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
@@ -572,12 +557,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>кольцевидно-овальное</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
@@ -597,20 +577,15 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
         <is>
           <t>не указано</t>
         </is>
@@ -632,20 +607,15 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>не указано</t>
         </is>
@@ -667,20 +637,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>не указано</t>
         </is>
@@ -702,22 +667,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>не указано</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
@@ -737,22 +697,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>не указано</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
@@ -772,137 +727,117 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>не указано</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>83</v>
+        <v>589</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>уд85_8-15_а.jpg</t>
+          <t>уд85_14-2_а.jpg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>подвеска</t>
+          <t>удила</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>овальное</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>не указано</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>84</v>
+        <v>590</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>уд85_8-15_б.jpg</t>
+          <t>уд85_14-2_б.jpg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>подвеска</t>
+          <t>удила</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>овальное</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>не указано</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>85</v>
+        <v>591</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>уд85_8-15_в.jpg</t>
+          <t>уд85_14-2_в.jpg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>подвеска</t>
+          <t>удила</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>овальное</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>не указано</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>589</v>
+        <v>632</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>уд85_14-2_а.jpg</t>
+          <t>уд85_17-2_а.jpg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -917,27 +852,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>трапециевидное кольчатое</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>не указано</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>590</v>
+        <v>633</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>уд85_14-2_б.jpg</t>
+          <t>уд85_17-2_б.jpg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -952,27 +882,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>трапециевидное кольчатое</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>не указано</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>591</v>
+        <v>634</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>уд85_14-2_в.jpg</t>
+          <t>уд85_17-3_а.jpg</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -987,27 +912,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>трапециевидное кольчатое</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>не указано</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>уд85_17-2_а.jpg</t>
+          <t>уд85_17-3_б.jpg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1017,32 +937,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>трапециевидное кольчатое</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>уд85_17-2_б.jpg</t>
+          <t>уд85_17-3_в.jpg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1052,32 +967,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>трапециевидное кольчатое</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>уд85_17-3_а.jpg</t>
+          <t>уд85_17-4_а.jpg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1087,32 +997,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>кольцевидное</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>уд85_17-3_б.jpg</t>
+          <t>уд85_17-4_б.jpg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1122,32 +1027,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>кольцевидное</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>уд85_17-3_в.jpg</t>
+          <t>уд85_17-4_в.jpg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1157,32 +1057,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>кольцевидное</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>уд85_17-4_а.jpg</t>
+          <t>уд85_17-5_а.jpg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1192,7 +1087,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1202,22 +1097,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>уд85_17-4_б.jpg</t>
+          <t>уд85_17-5_б.jpg</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1227,7 +1117,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1237,22 +1127,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>уд85_17-4_в.jpg</t>
+          <t>уд85_17-5_в.jpg</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1262,7 +1147,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1272,22 +1157,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>уд85_17-5_а.jpg</t>
+          <t>уд85_17-6_а.jpg</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1297,7 +1177,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1307,22 +1187,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>стремечковидные</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>уд85_17-5_б.jpg</t>
+          <t>уд85_17-6_б.jpg</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1332,7 +1207,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1342,22 +1217,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>стремечковидные</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>уд85_17-5_в.jpg</t>
+          <t>уд85_17-6_в.jpg</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1367,7 +1237,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1377,22 +1247,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>стремечковидные</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>уд85_17-6_а.jpg</t>
+          <t>уд85_18-1_а.jpg</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1402,32 +1267,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>с отдельной рамкой и округлым отверстием</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>уд85_17-6_б.jpg</t>
+          <t>уд85_18-1_б.jpg</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1437,32 +1297,27 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>с отдельной рамкой и округлым отверстием</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>уд85_17-6_в.jpg</t>
+          <t>уд85_18-1_в.jpg</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1472,32 +1327,27 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>с отдельной рамкой и округлым отверстием</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>уд85_18-1_а.jpg</t>
+          <t>уд85_18-1_г.jpg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1507,7 +1357,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1517,22 +1367,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">подтреугольно-кольчатое с округлым отверстием </t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>уд85_18-1_б.jpg</t>
+          <t>уд85_18-2_а.jpg</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1542,7 +1387,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1552,22 +1397,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">подтреугольно-кольчатое с округлым отверстием </t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>уд85_18-1_в.jpg</t>
+          <t>уд85_18-2_б.jpg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1577,7 +1417,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1587,22 +1427,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">подтреугольно-кольчатое с округлым отверстием </t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>уд85_18-1_г.jpg</t>
+          <t>уд85_18-2_в.jpg</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1612,7 +1447,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1622,22 +1457,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">подтреугольно-кольчатое с округлым отверстием </t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>уд85_18-2_а.jpg</t>
+          <t>уд85_18-2_г.jpg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1647,7 +1477,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1657,22 +1487,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>уд85_18-2_б.jpg</t>
+          <t>уд85_23-1_а.jpg</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1682,7 +1507,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1692,22 +1517,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>уд85_18-2_в.jpg</t>
+          <t>уд85_23-1_б.jpg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1717,7 +1537,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1727,22 +1547,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>уд85_18-2_г.jpg</t>
+          <t>уд85_23-1_в.jpg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1752,7 +1567,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1762,22 +1577,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>уд85_23-1_а.jpg</t>
+          <t>уд85_31-5_а.jpg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1787,32 +1597,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>не указано</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>уд85_23-1_б.jpg</t>
+          <t>уд85_31-5_б.jpg</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1822,32 +1627,27 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>не указано</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>656</v>
+        <v>798</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>уд85_23-1_в.jpg</t>
+          <t>уд85_41-5_а.jpg</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1857,32 +1657,27 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>не указано</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>665</v>
+        <v>799</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>уд85_31-5_а.jpg</t>
+          <t>уд85_41-5_б.jpg</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1892,32 +1687,27 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">подтреугольное с округлым отверстием </t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>666</v>
+        <v>800</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>уд85_31-5_б.jpg</t>
+          <t>уд85_41-5_в.jpg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1927,32 +1717,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">подтреугольное с округлым отверстием </t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>уд85_41-5_а.jpg</t>
+          <t>уд85_41-6_а.jpg</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1962,32 +1747,27 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">подтреугольное с округлым отверстием </t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>уд85_41-5_б.jpg</t>
+          <t>уд85_41-6_б.jpg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1997,32 +1777,27 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">подтреугольное с округлым отверстием </t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>уд85_41-5_в.jpg</t>
+          <t>уд85_41-6_в.jpg</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2032,32 +1807,27 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">подтреугольное с округлым отверстием </t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>уд85_41-6_а.jpg</t>
+          <t>уд85_15-6_field_1781679235796.jpg</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2067,32 +1837,27 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">овально-кольчатое с округлым отверстием </t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>уд85_41-6_б.jpg</t>
+          <t>уд85_15-6_field_1781679260000.jpg</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2102,137 +1867,117 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>железо</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">овально-кольчатое с округлым отверстием </t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>803</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>уд85_41-6_в.jpg</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>удила</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Бронза</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>смешанный</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">овально-кольчатое с округлым отверстием </t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+      <c r="A49" s="2" t="n">
+        <v>806</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>уд85_18-1_field_1781679418141.jpg</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>удила</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>бронза</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>целый</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>804</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>уд85_15-6_field_1781679235796.jpg</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>удила</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>железо</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>сломан</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>кольчатое</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+      <c r="A50" s="2" t="n">
+        <v>807</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>уд85_18-1_field_1781679434696.jpg</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>удила</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>бронза</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>целый</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>805</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>уд85_15-6_field_1781679260000.jpg</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>удила</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>железо</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>сломан</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>кольчатое</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+      <c r="A51" s="2" t="n">
+        <v>808</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>уд85_18-1_field_1781679619798.jpg</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>удила</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>бронза</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>целый</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="52" customFormat="1" s="2">
       <c r="A52" s="2" t="n">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781679418141.jpg</t>
+          <t>уд85_18-1_field_1781679679909.jpg</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2242,7 +1987,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2252,27 +1997,17 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>задвоено</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="53" customFormat="1" s="2">
       <c r="A53" s="2" t="n">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781679434696.jpg</t>
+          <t>уд85_18-2_field_1781679747248.jpg</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2282,7 +2017,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2292,22 +2027,17 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="54" customFormat="1" s="2">
       <c r="A54" s="2" t="n">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781679619798.jpg</t>
+          <t>уд85_18-2_field_1781679832322.jpg</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2317,7 +2047,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2327,22 +2057,17 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="55" customFormat="1" s="2">
       <c r="A55" s="2" t="n">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781679679909.jpg</t>
+          <t>уд85_18-1_field_1781680010036.jpg</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2352,7 +2077,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2362,22 +2087,17 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="56" customFormat="1" s="2">
       <c r="A56" s="2" t="n">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-2_field_1781679747248.jpg</t>
+          <t>уд85_18-1_field_1781680042474.jpg</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2387,7 +2107,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2397,22 +2117,17 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="57" customFormat="1" s="2">
       <c r="A57" s="2" t="n">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-2_field_1781679832322.jpg</t>
+          <t>уд85_18-2_field_1781680105182.jpg</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2422,7 +2137,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2432,22 +2147,17 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="58" customFormat="1" s="2">
       <c r="A58" s="2" t="n">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781680010036.jpg</t>
+          <t>уд85_18-2_field_1781680147358.jpg</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2457,7 +2167,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2467,22 +2177,17 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="59" customFormat="1" s="2">
       <c r="A59" s="2" t="n">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781680042474.jpg</t>
+          <t>уд85_18-1_field_1781680229760.jpg</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2492,7 +2197,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2502,22 +2207,17 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="60" customFormat="1" s="2">
       <c r="A60" s="2" t="n">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-2_field_1781680105182.jpg</t>
+          <t>уд85_18-1_field_1781680264370.jpg</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2527,7 +2227,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2537,22 +2237,17 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="61" customFormat="1" s="2">
       <c r="A61" s="2" t="n">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-2_field_1781680147358.jpg</t>
+          <t>уд85_18-1_field_1781680337228.jpg</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2562,7 +2257,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2572,22 +2267,17 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="62" customFormat="1" s="2">
       <c r="A62" s="2" t="n">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781680229760.jpg</t>
+          <t>уд85_18-1_field_1781680358906.jpg</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2597,7 +2287,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2607,22 +2297,17 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="63" customFormat="1" s="2">
       <c r="A63" s="2" t="n">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781680264370.jpg</t>
+          <t>уд85_18-1_field_1781680425482.jpg</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2632,7 +2317,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2642,22 +2327,17 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="64" customFormat="1" s="2">
       <c r="A64" s="2" t="n">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781680337228.jpg</t>
+          <t>уд85_18-1_field_1781680462449.jpg</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2667,7 +2347,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2677,22 +2357,17 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="65" customFormat="1" s="2">
       <c r="A65" s="2" t="n">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781680358906.jpg</t>
+          <t>уд85_18-1_field_1781680532745.jpg</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -2702,7 +2377,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2712,22 +2387,17 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="66" customFormat="1" s="2">
       <c r="A66" s="2" t="n">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781680425482.jpg</t>
+          <t>уд85_18-1_field_1781680571738.jpg</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -2737,7 +2407,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2747,22 +2417,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="67" customFormat="1" s="2">
       <c r="A67" s="2" t="n">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781680462449.jpg</t>
+          <t>уд85_18-1_field_1781680611274.jpg</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2772,7 +2437,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2782,22 +2447,17 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="68" customFormat="1" s="2">
       <c r="A68" s="2" t="n">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781680532745.jpg</t>
+          <t>уд85_18-1_field_1781680642872.jpg</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2807,7 +2467,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2817,22 +2477,17 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="69" customFormat="1" s="2">
       <c r="A69" s="2" t="n">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781680571738.jpg</t>
+          <t>уд85_18-1_field_1781680687497.jpg</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2842,7 +2497,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2852,22 +2507,17 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="70" customFormat="1" s="2">
       <c r="A70" s="2" t="n">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781680611274.jpg</t>
+          <t>уд85_18-1_field_1781680713570.jpg</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2877,7 +2527,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2887,22 +2537,17 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="71" customFormat="1" s="2">
       <c r="A71" s="2" t="n">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781680642872.jpg</t>
+          <t>уд85_41-6_field_1781680771018.jpg</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2912,32 +2557,27 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="72" customFormat="1" s="2">
       <c r="A72" s="2" t="n">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781680687497.jpg</t>
+          <t>уд85_41-6_field_1781680805509.jpg</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2947,32 +2587,27 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="73" customFormat="1" s="2">
       <c r="A73" s="2" t="n">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>уд85_18-1_field_1781680713570.jpg</t>
+          <t>уд85_41-6_field_1781680842483.jpg</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2982,32 +2617,27 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>целый</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>подтреугольно-кольчатое</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="74" customFormat="1" s="2">
       <c r="A74" s="2" t="n">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>уд85_41-6_field_1781680771018.jpg</t>
+          <t>уд85_41-6_field_1781680861291.jpg</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3017,32 +2647,27 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="75" customFormat="1" s="2">
       <c r="A75" s="2" t="n">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>уд85_41-6_field_1781680805509.jpg</t>
+          <t>уд85_41-6_field_1781680902669.jpg</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3052,32 +2677,27 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="76" customFormat="1" s="2">
       <c r="A76" s="2" t="n">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>уд85_41-6_field_1781680842483.jpg</t>
+          <t>уд85_41-6_field_1781680925550.jpg</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3087,32 +2707,27 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="77" customFormat="1" s="2">
       <c r="A77" s="2" t="n">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>уд85_41-6_field_1781680861291.jpg</t>
+          <t>уд85_41-6_field_1781680958014.jpg</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3122,32 +2737,27 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="78" customFormat="1" s="2">
       <c r="A78" s="2" t="n">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>уд85_41-6_field_1781680902669.jpg</t>
+          <t>уд85_41-6_field_1781680978984.jpg</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3157,32 +2767,27 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="79" customFormat="1" s="2">
       <c r="A79" s="2" t="n">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>уд85_41-6_field_1781680925550.jpg</t>
+          <t>уд85_41-5_field_1781681012430.jpg</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3192,32 +2797,27 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="80" customFormat="1" s="2">
       <c r="A80" s="2" t="n">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>уд85_41-6_field_1781680958014.jpg</t>
+          <t>уд85_41-5_field_1781681031542.jpg</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -3227,32 +2827,27 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="81" customFormat="1" s="2">
       <c r="A81" s="2" t="n">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>уд85_41-6_field_1781680978984.jpg</t>
+          <t>уд85_41-5_field_1781681064670.jpg</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3262,32 +2857,27 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+          <t>подтреугольное</t>
         </is>
       </c>
     </row>
     <row r="82" customFormat="1" s="2">
       <c r="A82" s="2" t="n">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>уд85_41-5_field_1781681012430.jpg</t>
+          <t>уд85_41-5_field_1781681083822.jpg</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3297,32 +2887,27 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
           <t>подтреугольное</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
         </is>
       </c>
     </row>
     <row r="83" customFormat="1" s="2">
       <c r="A83" s="2" t="n">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>уд85_41-5_field_1781681031542.jpg</t>
+          <t>уд85_41-5_field_1781681118220.jpg</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3332,32 +2917,27 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
           <t>подтреугольное</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
         </is>
       </c>
     </row>
     <row r="84" customFormat="1" s="2">
       <c r="A84" s="2" t="n">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>уд85_41-5_field_1781681064670.jpg</t>
+          <t>уд85_41-5_field_1781681142964.jpg</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3367,32 +2947,27 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
           <t>подтреугольное</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
         </is>
       </c>
     </row>
     <row r="85" customFormat="1" s="2">
       <c r="A85" s="2" t="n">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>уд85_41-5_field_1781681083822.jpg</t>
+          <t>уд85_41-5_field_1781681180084.jpg</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3402,32 +2977,27 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
           <t>подтреугольное</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
         </is>
       </c>
     </row>
     <row r="86" customFormat="1" s="2">
       <c r="A86" s="2" t="n">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>уд85_41-5_field_1781681118220.jpg</t>
+          <t>уд85_41-5_field_1781681207782.jpg</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -3437,12 +3007,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>смешанный</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -3450,327 +3020,68 @@
           <t>подтреугольное</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
-        </is>
-      </c>
     </row>
     <row r="87" customFormat="1" s="2">
-      <c r="A87" s="2" t="n">
-        <v>841</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>уд85_41-5_field_1781681142964.jpg</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>удила</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Бронза</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>смешанный</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>подтреугольное</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
+      <c r="A87" t="n">
+        <v>848</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>уд85_18-2_field_1781681697302.jpg</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>удила</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>бронза</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>сломан</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>кольчато-овальное</t>
         </is>
       </c>
     </row>
     <row r="88" customFormat="1" s="2">
-      <c r="A88" s="2" t="n">
-        <v>842</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>уд85_41-5_field_1781681180084.jpg</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>удила</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Бронза</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>смешанный</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>подтреугольное</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" customFormat="1" s="2">
-      <c r="A89" s="2" t="n">
-        <v>843</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>уд85_41-5_field_1781681207782.jpg</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>удила</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Бронза</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>смешанный</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>подтреугольное</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>шарнирные</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>844</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>уд85_12-15_field_1781681457283.jpg</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>псалии</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>бронза</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>смешанный</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>845</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>уд85_12-15_field_1781681505602.jpg</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>псалии</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>бронза</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>смешанный</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>846</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>уд85_12-15_field_1781681539112.jpg</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>псалии</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>бронза</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>смешанный</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>847</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>уд85_12-15_field_1781681565002.jpg</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>псалии</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>бронза</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>смешанный</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>848</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>уд85_18-2_field_1781681697302.jpg</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>удила</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Бронза</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Фрагмент</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
+      <c r="A88" t="n">
         <v>849</v>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>уд85_18-2_field_1781681717749.jpg</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>удила</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Бронза</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Фрагмент</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>овально-кольчатое</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-    </row>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>удила</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>бронза</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>сломан</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>кольчато-овальное</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" customFormat="1" s="2"/>
   </sheetData>
   <autoFilter ref="A1:H95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
